--- a/scratch/student_scores.xlsx
+++ b/scratch/student_scores.xlsx
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -444,14 +444,12 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>P101v0101
-(기초1)</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>P101v0102
-(기초2)</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
@@ -467,85 +465,10 @@
       <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Feedback</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="n">
-        <v>1</v>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>tester</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
-        <v>100</v>
-      </c>
-      <c r="D2" t="n">
-        <v>90</v>
-      </c>
-      <c r="E2" t="n">
-        <v>190</v>
-      </c>
-      <c r="F2" t="n">
-        <v>95</v>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>통과</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="C2">
-    <cfRule type="colorScale" priority="1">
-      <colorScale>
-        <cfvo type="num" val="0"/>
-        <cfvo type="num" val="50"/>
-        <cfvo type="num" val="100"/>
-        <color rgb="00FF6347"/>
-        <color rgb="00FFD700"/>
-        <color rgb="0090EE90"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D2">
-    <cfRule type="colorScale" priority="1">
-      <colorScale>
-        <cfvo type="num" val="0"/>
-        <cfvo type="num" val="50"/>
-        <cfvo type="num" val="100"/>
-        <color rgb="00FF6347"/>
-        <color rgb="00FFD700"/>
-        <color rgb="0090EE90"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E2">
-    <cfRule type="colorScale" priority="1">
-      <colorScale>
-        <cfvo type="num" val="0"/>
-        <cfvo type="num" val="50"/>
-        <cfvo type="num" val="100"/>
-        <color rgb="00FF6347"/>
-        <color rgb="00FFD700"/>
-        <color rgb="0090EE90"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F2">
-    <cfRule type="colorScale" priority="1">
-      <colorScale>
-        <cfvo type="num" val="0"/>
-        <cfvo type="num" val="50"/>
-        <cfvo type="num" val="100"/>
-        <color rgb="00FF6347"/>
-        <color rgb="00FFD700"/>
-        <color rgb="0090EE90"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>